--- a/reports/2026-06-23.xlsx
+++ b/reports/2026-06-23.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99999.69998799999</v>
+        <v>99999.754988</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.008731981719381119</v>
+        <v>-0.0121710358552735</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008731981719381119</v>
+        <v>0.0121710358552735</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -521,17 +521,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>373.2653717333333</v>
+        <v>201.700699</v>
       </c>
       <c r="D2" t="n">
-        <v>373.2653717333333</v>
+        <v>201.700699</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +597,41 @@
           <t>ts</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cd856b9a-9902-4f31-892a-cbbdb50e2de7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E2" t="n">
+        <v>201.700699</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.93919753</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/2026-06-23.xlsx
+++ b/reports/2026-06-23.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99999.754988</v>
+        <v>99920.92971647851</v>
       </c>
       <c r="C2" t="n">
+        <v>-78.75527752148406</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.01386371004599338</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01307553405779002</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.0121710358552735</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0121710358552735</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>201.700699</v>
+        <v>201.5250776666667</v>
       </c>
       <c r="D2" t="n">
-        <v>201.700699</v>
+        <v>200.2749938964844</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-78.75527752148406</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,41 +597,6 @@
           <t>ts</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>cd856b9a-9902-4f31-892a-cbbdb50e2de7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>49</v>
-      </c>
-      <c r="E2" t="n">
-        <v>201.700699</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.93919753</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FILLED</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
